--- a/inst/extdata/Input_Data.xlsx
+++ b/inst/extdata/Input_Data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpala\Documents\StablePopulation\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B87D521-12F1-4F12-A612-DBD9B95BEEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784E1A72-7AB5-4093-A83C-625D4930CD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demografia_Castor_canadensis" sheetId="1" r:id="rId1"/>
+    <sheet name="pepito" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>Age (years)</t>
   </si>
@@ -967,4 +968,148 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A27010-651C-4812-8353-E59E9F4E6109}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.89500000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>1.244</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1.282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>1.387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>